--- a/Simone_Cavallero/Invaders_Realizations/Code/output/AC_n3.xlsx
+++ b/Simone_Cavallero/Invaders_Realizations/Code/output/AC_n3.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI2"/>
+  <dimension ref="A1:AE4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,150 +456,130 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>F4</t>
+          <t>M1</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>F5</t>
+          <t>M2</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>F6</t>
+          <t>M3</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>M1</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>M2</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>M3</t>
+          <t>W3</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>M4</t>
+          <t>EM1</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>M5</t>
+          <t>EM2</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>M6</t>
+          <t>EM3</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
+          <t>X1</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>X2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>X3</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>X4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>X5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>X6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>X7</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>X8</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
           <t>R1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>R2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>R3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>R4</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>W1</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>W2</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>W3</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>W4</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>W5</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>W6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>EM1</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>EM2</t>
-        </is>
-      </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>EM3</t>
+          <t>R5</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>EM4</t>
+          <t>R6</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>EM5</t>
+          <t>R7</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>EM6</t>
+          <t>R8</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>X1</t>
-        </is>
-      </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>X2</t>
-        </is>
-      </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>X3</t>
-        </is>
-      </c>
-      <c r="AH1" s="1" t="inlineStr">
-        <is>
-          <t>X4</t>
-        </is>
-      </c>
-      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Zeroes</t>
         </is>
@@ -613,7 +593,7 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -622,13 +602,13 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -643,19 +623,19 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -667,7 +647,7 @@
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -688,10 +668,10 @@
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -699,17 +679,195 @@
       <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
